--- a/SGC-CKN/Excel/ed58ef21-5c6e-4e69-8653-31c41b8c1493_Hạng_mục_Lô_CT-02_D7-19_D800_22-05-2026.xlsx
+++ b/SGC-CKN/Excel/ed58ef21-5c6e-4e69-8653-31c41b8c1493_Hạng_mục_Lô_CT-02_D7-19_D800_22-05-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>D7-19</t>
+    <t>P7-79</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -1212,7 +1212,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.57</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-6.5</v>
@@ -1221,10 +1221,10 @@
         <v>0.42</v>
       </c>
       <c r="I11" s="5">
-        <v>5.93</v>
+        <v>6.5</v>
       </c>
       <c r="J11" s="8">
-        <v>14.23</v>
+        <v>15.6</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1355,16 +1355,16 @@
         <v>-22</v>
       </c>
       <c r="G15" s="18">
-        <v>-26.4</v>
+        <v>-26.1</v>
       </c>
       <c r="H15" s="18">
         <v>0.25</v>
       </c>
       <c r="I15" s="18">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J15" s="8">
-        <v>17.6</v>
+        <v>16.4</v>
       </c>
       <c r="K15" s="19" t="s">
         <v>30</v>
@@ -1387,7 +1387,7 @@
         <v>45</v>
       </c>
       <c r="F16" s="21">
-        <v>-26.4</v>
+        <v>-26.1</v>
       </c>
       <c r="G16" s="21">
         <v>-34.1</v>
@@ -1396,10 +1396,10 @@
         <v>0.17</v>
       </c>
       <c r="I16" s="21">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="J16" s="8">
-        <v>46.2</v>
+        <v>48</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>30</v>
@@ -1460,7 +1460,7 @@
         <v>-37.1</v>
       </c>
       <c r="G18" s="27">
-        <v>-39</v>
+        <v>-39.00000000000009</v>
       </c>
       <c r="H18" s="27">
         <v>0.2</v>
@@ -1492,19 +1492,19 @@
         <v>55</v>
       </c>
       <c r="F19" s="30">
-        <v>-39</v>
+        <v>-39.00000000000009</v>
       </c>
       <c r="G19" s="30">
-        <v>-44.2</v>
+        <v>-43.55</v>
       </c>
       <c r="H19" s="30">
         <v>4</v>
       </c>
       <c r="I19" s="30">
-        <v>5.2</v>
+        <v>4.55</v>
       </c>
       <c r="J19" s="33">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="K19" s="31" t="s">
         <v>56</v>
@@ -1527,19 +1527,19 @@
         <v>59</v>
       </c>
       <c r="F20" s="34">
-        <v>-44.2</v>
+        <v>-43.55</v>
       </c>
       <c r="G20" s="34">
-        <v>-44.2</v>
+        <v>-52.02</v>
       </c>
       <c r="H20" s="34">
         <v>0.42</v>
       </c>
       <c r="I20" s="34">
-        <v>0</v>
-      </c>
-      <c r="J20" s="33">
-        <v>0</v>
+        <v>8.47</v>
+      </c>
+      <c r="J20" s="8">
+        <v>20.33</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>60</v>
@@ -1694,7 +1694,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.57</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-6.5</v>
@@ -1703,10 +1703,10 @@
         <v>0.42</v>
       </c>
       <c r="H2" s="5">
-        <v>5.93</v>
+        <v>6.5</v>
       </c>
       <c r="I2" s="8">
-        <v>14.23</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1813,16 +1813,16 @@
         <v>-22</v>
       </c>
       <c r="F6" s="18">
-        <v>-26.4</v>
+        <v>-26.1</v>
       </c>
       <c r="G6" s="18">
         <v>0.25</v>
       </c>
       <c r="H6" s="18">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I6" s="8">
-        <v>17.6</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1839,7 +1839,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="21">
-        <v>-26.4</v>
+        <v>-26.1</v>
       </c>
       <c r="F7" s="21">
         <v>-34.1</v>
@@ -1848,10 +1848,10 @@
         <v>0.17</v>
       </c>
       <c r="H7" s="21">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="I7" s="8">
-        <v>46.2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1929,16 +1929,16 @@
         <v>-39</v>
       </c>
       <c r="F10" s="30">
-        <v>-44.2</v>
+        <v>-43.55</v>
       </c>
       <c r="G10" s="30">
         <v>4</v>
       </c>
       <c r="H10" s="30">
-        <v>5.2</v>
+        <v>4.55</v>
       </c>
       <c r="I10" s="33">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1955,19 +1955,19 @@
         <v>1</v>
       </c>
       <c r="E11" s="34">
-        <v>-44.2</v>
+        <v>-43.55</v>
       </c>
       <c r="F11" s="34">
-        <v>-44.2</v>
+        <v>-52.02</v>
       </c>
       <c r="G11" s="34">
         <v>0.42</v>
       </c>
       <c r="H11" s="34">
-        <v>0</v>
-      </c>
-      <c r="I11" s="33">
-        <v>0</v>
+        <v>8.47</v>
+      </c>
+      <c r="I11" s="8">
+        <v>20.33</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1984,19 +1984,19 @@
         <v>10</v>
       </c>
       <c r="E12" s="39">
-        <v>-0.57</v>
+        <v>0</v>
       </c>
       <c r="F12" s="39">
-        <v>-44.2</v>
+        <v>-52.02</v>
       </c>
       <c r="G12" s="39">
         <v>7.33</v>
       </c>
       <c r="H12" s="39">
-        <v>43.63</v>
+        <v>52.02</v>
       </c>
       <c r="I12" s="39">
-        <v>5.95</v>
+        <v>7.09</v>
       </c>
     </row>
   </sheetData>
